--- a/assets-source/reports/qto-quantities.xlsx
+++ b/assets-source/reports/qto-quantities.xlsx
@@ -631,11 +631,11 @@
       </c>
       <c r="B2" s="3">
         <f>'כתב כמויות'!B8</f>
-        <v>98.91</v>
+        <v>49.46</v>
       </c>
       <c r="C2" s="3">
         <f>'כתב כמויות'!D8</f>
-        <v>98.91</v>
+        <v>49.46</v>
       </c>
       <c r="D2" s="3">
         <f>'כתב כמויות'!B9</f>
@@ -668,11 +668,11 @@
       </c>
       <c r="B3" s="5">
         <f>ROUND(SUM(B2:B2),2)</f>
-        <v>98.91</v>
+        <v>49.46</v>
       </c>
       <c r="C3" s="5">
         <f>ROUND(SUM(C2:C2),2)</f>
-        <v>98.91</v>
+        <v>49.46</v>
       </c>
       <c r="D3" s="5">
         <f>ROUND(SUM(D2:D2),2)</f>
@@ -786,7 +786,7 @@
         <v>27</v>
       </c>
       <c r="C2" s="3">
-        <v>25.48</v>
+        <v>12.74</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>28</v>
@@ -811,7 +811,7 @@
       </c>
       <c r="K2" s="3">
         <f>IF(ISNUMBER(C2),ROUND(C2*(1+IF(ISNUMBER(G2),G2,0)/100),2),"—")</f>
-        <v>25.48</v>
+        <v>12.74</v>
       </c>
       <c r="L2" s="3" t="str">
         <f>IF(ISNUMBER(D2),ROUND(D2*(1+IF(ISNUMBER(H2),H2,0)/100),2),"—")</f>
@@ -844,7 +844,7 @@
         <v>30</v>
       </c>
       <c r="C3" s="8">
-        <v>26.21</v>
+        <v>13.11</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>28</v>
@@ -869,7 +869,7 @@
       </c>
       <c r="K3" s="8">
         <f>IF(ISNUMBER(C3),ROUND(C3*(1+IF(ISNUMBER(G3),G3,0)/100),2),"—")</f>
-        <v>26.21</v>
+        <v>13.11</v>
       </c>
       <c r="L3" s="8" t="str">
         <f>IF(ISNUMBER(D3),ROUND(D3*(1+IF(ISNUMBER(H3),H3,0)/100),2),"—")</f>
@@ -902,7 +902,7 @@
         <v>31</v>
       </c>
       <c r="C4" s="3">
-        <v>47.22</v>
+        <v>23.61</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>28</v>
@@ -927,7 +927,7 @@
       </c>
       <c r="K4" s="3">
         <f>IF(ISNUMBER(C4),ROUND(C4*(1+IF(ISNUMBER(G4),G4,0)/100),2),"—")</f>
-        <v>47.22</v>
+        <v>23.61</v>
       </c>
       <c r="L4" s="3" t="str">
         <f>IF(ISNUMBER(D4),ROUND(D4*(1+IF(ISNUMBER(H4),H4,0)/100),2),"—")</f>
@@ -983,12 +983,12 @@
       </c>
       <c r="B8" s="13">
         <f>ROUND(SUM(C2:C4),2)</f>
-        <v>98.91</v>
+        <v>49.46</v>
       </c>
       <c r="C8" s="12"/>
       <c r="D8" s="13">
         <f>ROUND(SUM(K2:K4),2)</f>
-        <v>98.91</v>
+        <v>49.46</v>
       </c>
       <c r="E8" s="12"/>
       <c r="F8" s="12"/>
